--- a/Layout-requirements-template.xlsx
+++ b/Layout-requirements-template.xlsx
@@ -176,7 +176,7 @@
     <t>Comments</t>
   </si>
   <si>
-    <t xml:space="preserve">For all other nets, that is starting with "D_" prefix, use 0.3mm trace. Placement order for connectors J901 to J912, along with silk screen label is specified on page 9. </t>
+    <t xml:space="preserve">For all other nets, that is starting with "D_" prefix, use 0.3mm trace. Placement order for connectors J901 to J912, along with silk screen label is specified on page 9. The connectors must be placed at the edges and the mounting holes at each corner.</t>
   </si>
   <si>
     <t xml:space="preserve">Silkscreen Information</t>
